--- a/HCVData/subtyping-comparison/12-report-subtype-disagreements/Subtype_Disagreement_Reports.xlsx
+++ b/HCVData/subtyping-comparison/12-report-subtype-disagreements/Subtype_Disagreement_Reports.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="483">
   <si>
     <t>CometSubtype</t>
   </si>
@@ -41,1000 +41,1402 @@
     <t>1A</t>
   </si>
   <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>1A;1B;1C;1J;1K;1M;1N;1O;1P;3A</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>192</t>
   </si>
   <si>
+    <t>1A;1B;1C;1D;1H;1I;1K;1M;1N;1O;2L;3A;6D;6P;6XD;6XF;6XG;7B</t>
+  </si>
+  <si>
+    <t>1C</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1A;1C;1O</t>
+  </si>
+  <si>
+    <t>1E</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1A;1B;1E</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1A;1B;1G</t>
+  </si>
+  <si>
+    <t>1H</t>
+  </si>
+  <si>
+    <t>1B;1C;1H</t>
+  </si>
+  <si>
+    <t>1L</t>
+  </si>
+  <si>
+    <t>1B;1L</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2A;2C;2M;2Q;2R;2U</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>1K;2B;2C;2L;2Q;2T;7B</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>2C;2F;2Q</t>
+  </si>
+  <si>
+    <t>2I</t>
+  </si>
+  <si>
+    <t>2I;2K</t>
+  </si>
+  <si>
+    <t>2J</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>2A;2C;2D;2E;2F;2I;2J;2K;2M;2Q;2R;2T;2U;2V;3A;5A;7A;7B</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>2D;2J;2K;2Q</t>
+  </si>
+  <si>
+    <t>2Q</t>
+  </si>
+  <si>
+    <t>2K;2Q</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>1A;1B;3A;3D;3E</t>
+  </si>
+  <si>
+    <t>3G</t>
+  </si>
+  <si>
+    <t>3B;3G;3I</t>
+  </si>
+  <si>
+    <t>3H</t>
+  </si>
+  <si>
+    <t>3H;8A</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>4A;4C;4E;4O;4P</t>
+  </si>
+  <si>
+    <t>4D</t>
+  </si>
+  <si>
+    <t>4A;4D</t>
+  </si>
+  <si>
+    <t>4F</t>
+  </si>
+  <si>
+    <t>4C;4E;4F;4Q</t>
+  </si>
+  <si>
+    <t>4G?</t>
+  </si>
+  <si>
+    <t>4G;4G?</t>
+  </si>
+  <si>
+    <t>4K</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4B;4G;4H;4K;4R;6Q</t>
+  </si>
+  <si>
+    <t>4L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4A;4L;4V</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>1B;4M</t>
+  </si>
+  <si>
+    <t>4R</t>
+  </si>
+  <si>
+    <t>4A;4R</t>
+  </si>
+  <si>
+    <t>4V</t>
+  </si>
+  <si>
+    <t>2L;4B;4Q;4V</t>
+  </si>
+  <si>
+    <t>4W</t>
+  </si>
+  <si>
+    <t>4B;4W</t>
+  </si>
+  <si>
+    <t>5A</t>
+  </si>
+  <si>
+    <t>2L;5A</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>6A;6B;6XD</t>
+  </si>
+  <si>
+    <t>6C</t>
+  </si>
+  <si>
+    <t>1H;6C</t>
+  </si>
+  <si>
+    <t>6D</t>
+  </si>
+  <si>
+    <t>1H;6D;8A</t>
+  </si>
+  <si>
+    <t>6E</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>1B;1C;6C;6E;6EZ;6Q;6U;6XC;6XF;8A</t>
+  </si>
+  <si>
+    <t>6G</t>
+  </si>
+  <si>
+    <t>6H</t>
+  </si>
+  <si>
+    <t>5A;6H;8A</t>
+  </si>
+  <si>
+    <t>6K</t>
+  </si>
+  <si>
+    <t>6K;6K-RELATED;6XI;8A</t>
+  </si>
+  <si>
+    <t>6L</t>
+  </si>
+  <si>
     <t>19</t>
   </si>
   <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>1A;1B;1J;1K;1M;1N;1O;2B;3A;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1A-1C;UNASSIGNED_1, 1A-2B;UNASSIGNED_1, 1A-3A;UNASSIGNED_1, 1A-4A;UNASSIGNED_1, 1A-4A-4V</t>
-  </si>
-  <si>
-    <t>1B</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1H;1I;1K;1M;1N;1O;1P;2B;2J;2K;2K1B;3A;5A;6D;6E;6G;6H;6N;6P;6S;6W;6XA;6XD;6XF;6XG;6XH;7A;7B;8A;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1B-1A;UNASSIGNED_1, 1B-2A;UNASSIGNED_1, 1B-2A-2K;UNASSIGNED_1, 1B-2B;UNASSIGNED_1, 1B-2B-6D-6B;UNASSIGNED_1, 1B-2J-2A-2B;UNASSIGNED_1, 1B-2J-2A-2J-2Q-2K-2Q-2K;UNASSIGNED_1, 1B-2J-2K;UNASSIGNED_1, 1B-2J-2Q-2K;UNASSIGNED_1, 1B-2K;UNASSIGNED_1, 1B-3B;UNASSIGNED_1, 1B-3H;UNASSIGNED_1, 1B-6B;UNASSIGNED_1, 1B-6D-6B;UNASSIGNED_1, 1B-6H-2A-6H-6D-3G;UNASSIGNED_1, 1B-6H-6B;UNASSIGNED_1, 1B-6K-6B;UNASSIGNED_1, 1B-6K-6D-6B;UNASSIGNED_1, 1B-6W;UNASSIGNED_1, 2B-1B;UNASSIGNED_1, 2J-5A;UNASSIGNED_1, 2K-1B;UNASSIGNED_1, 6G-3B</t>
-  </si>
-  <si>
-    <t>1C</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1A;1C;1M;1O</t>
-  </si>
-  <si>
-    <t>1E</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1A;1B;1E;UNASSIGNED_1, 1E-4K-4N-4G-4A-4F-4D-4G</t>
-  </si>
-  <si>
-    <t>1G</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1A;1B;1G</t>
-  </si>
-  <si>
-    <t>1H</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1B;1C;1H;UNASSIGNED_1, 1H-4F-4L-4F</t>
-  </si>
-  <si>
-    <t>1L</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>1A;6K;6K-RELATED;6L;6L-RELATED;6XB;6XI;6XJ;8A</t>
+  </si>
+  <si>
+    <t>6M</t>
+  </si>
+  <si>
+    <t>6M;8A</t>
+  </si>
+  <si>
+    <t>6N</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>6N;6XE;6XG</t>
+  </si>
+  <si>
+    <t>6O</t>
+  </si>
+  <si>
+    <t>6O;6Q</t>
+  </si>
+  <si>
+    <t>6Q</t>
+  </si>
+  <si>
+    <t>1A;6Q</t>
+  </si>
+  <si>
+    <t>6R</t>
+  </si>
+  <si>
+    <t>1K;6R</t>
+  </si>
+  <si>
+    <t>6S</t>
+  </si>
+  <si>
+    <t>1J;6S</t>
+  </si>
+  <si>
+    <t>6W</t>
+  </si>
+  <si>
+    <t>2L;2T;5A;6A;6D;6G;6H;6L;6N;6Q;6S;6W;6XA;6XD;6XF;6XH;8A</t>
+  </si>
+  <si>
+    <t>6XA</t>
+  </si>
+  <si>
+    <t>6U;6XA</t>
+  </si>
+  <si>
+    <t>7A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-1B</t>
+  </si>
+  <si>
+    <t>1A;1B;1K;1N;UNASSIGNED_1, 1A-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-1C</t>
+  </si>
+  <si>
+    <t>1A;1O;UNASSIGNED_1, 1A-1C</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-1L</t>
+  </si>
+  <si>
+    <t>1A;1L;UNASSIGNED_1, 1A-1L</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-2B</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1A;2B;UNASSIGNED_1, 1A-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-3A</t>
+  </si>
+  <si>
+    <t>1A;UNASSIGNED_1, 1A-3A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-4A</t>
+  </si>
+  <si>
+    <t>1A;1P;UNASSIGNED_1, 1A-4A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-4A-4V</t>
+  </si>
+  <si>
+    <t>1A;UNASSIGNED_1, 1A-4A-4V</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1A-4D</t>
+  </si>
+  <si>
+    <t>1A;UNASSIGNED_1, 1A-4D</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-1A</t>
+  </si>
+  <si>
+    <t>1A;1B;1I;1P;UNASSIGNED_1, 1B-1A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2A</t>
+  </si>
+  <si>
+    <t>1B;1I;UNASSIGNED_1, 1B-2A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2A-2K</t>
+  </si>
+  <si>
+    <t>1B;2K;UNASSIGNED_1, 1B-2A-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2B</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>1B;1L;UNASSIGNED_1, 1A-1L;UNASSIGNED_1, 1L-1A;UNASSIGNED_1, 1L-1A-1B;UNASSIGNED_1, 1L-2A;UNASSIGNED_1, 1L-2K-2A;UNASSIGNED_1, 1L-2K-2J-2A-2Q;UNASSIGNED_1, 1L-4F;UNASSIGNED_1, 1L-4V-4F</t>
-  </si>
-  <si>
-    <t>2A</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>2A;2J;2M;2Q;2U;2V;7A;UNASSIGNED_1, 2A-2K;UNASSIGNED_1, 2A-3A</t>
-  </si>
-  <si>
-    <t>2B</t>
+    <t>1B;2B;UNASSIGNED_1, 1B-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2B-6D-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-2B-6D-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2J-2A-2B</t>
+  </si>
+  <si>
+    <t>1B;2B;UNASSIGNED_1, 1B-2J-2A-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2J-2A-2J-2Q-2K-2Q-2K</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-2J-2A-2J-2Q-2K-2Q-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2J-2K</t>
+  </si>
+  <si>
+    <t>1B;2K;UNASSIGNED_1, 1B-2J-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2J-2Q-2K</t>
+  </si>
+  <si>
+    <t>1B;2K;UNASSIGNED_1, 1B-2J-2Q-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2K</t>
+  </si>
+  <si>
+    <t>1B;2K;2K1B;UNASSIGNED_1, 1B-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-3B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-3B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-3H</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6D-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6D-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6H-2A-6H-6D-3G</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6H-2A-6H-6D-3G</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6H-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6H-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6K-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6K-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6K-6D-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6K-6D-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6W</t>
+  </si>
+  <si>
+    <t>8A;UNASSIGNED_1, 1B-6W</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1E-4K-4N-4G-4A-4F-4D-4G</t>
+  </si>
+  <si>
+    <t>1E;UNASSIGNED_1, 1E-4K-4N-4G-4A-4F-4D-4G</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1H-4F-4L-4F</t>
+  </si>
+  <si>
+    <t>1H;UNASSIGNED_1, 1H-4F-4L-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-1A</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-1A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-1A-1B</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-1A-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-2A</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-2A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-2K-2A</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-2K-2A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-2K-2J-2A-2Q</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-2K-2J-2A-2Q</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-4F</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-4V-4F</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-4V-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2A-2K</t>
+  </si>
+  <si>
+    <t>2M;2Q;UNASSIGNED_1, 2A-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2A-3A</t>
+  </si>
+  <si>
+    <t>2A;UNASSIGNED_1, 2A-3A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2B-1B</t>
+  </si>
+  <si>
+    <t>1B;2B;UNASSIGNED_1, 2B-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2B-2D</t>
+  </si>
+  <si>
+    <t>2B;2D;UNASSIGNED_1, 2B-2D</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2C-2B-3G-2B-2A</t>
+  </si>
+  <si>
+    <t>2C;UNASSIGNED_1, 2C-2B-3G-2B-2A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2C-6H-2B</t>
+  </si>
+  <si>
+    <t>2C;UNASSIGNED_1, 2C-6H-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2C-6H-3H</t>
+  </si>
+  <si>
+    <t>2C;UNASSIGNED_1, 2C-6H-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2D-2A</t>
+  </si>
+  <si>
+    <t>2D;UNASSIGNED_1, 2D-2A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2I-2K</t>
+  </si>
+  <si>
+    <t>2I;UNASSIGNED_1, 2I-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2I-2K-2B-3H</t>
+  </si>
+  <si>
+    <t>2I;UNASSIGNED_1, 2I-2K-2B-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2I-2K-2C-3H</t>
+  </si>
+  <si>
+    <t>2I;UNASSIGNED_1, 2I-2K-2C-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2J-5A</t>
+  </si>
+  <si>
+    <t>8A;UNASSIGNED_1, 2J-5A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2J-6K</t>
+  </si>
+  <si>
+    <t>2J;UNASSIGNED_1, 2J-6K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2K-1B</t>
+  </si>
+  <si>
+    <t>1B;2K;UNASSIGNED_1, 2K-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3A-1A</t>
+  </si>
+  <si>
+    <t>3A;UNASSIGNED_1, 3A-1A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3A-2B</t>
+  </si>
+  <si>
+    <t>3A;UNASSIGNED_1, 3A-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3A-3G</t>
+  </si>
+  <si>
+    <t>3H;3I;UNASSIGNED_1, 3A-3G</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3A-3H</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>3A;UNASSIGNED_1, 3A-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3B-3A</t>
+  </si>
+  <si>
+    <t>3B;UNASSIGNED_1, 3B-3A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3B-3H</t>
+  </si>
+  <si>
+    <t>3B;UNASSIGNED_1, 3B-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3H-6A</t>
+  </si>
+  <si>
+    <t>1K;3H;UNASSIGNED_1, 3H-6A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3I-3H-6H-6B</t>
+  </si>
+  <si>
+    <t>3I;UNASSIGNED_1, 3I-3H-6H-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 3I-3K</t>
+  </si>
+  <si>
+    <t>3I;UNASSIGNED_1, 3I-3K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4A-1A</t>
+  </si>
+  <si>
+    <t>4A;UNASSIGNED_1, 4A-1A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4D-4A-4N-4G-1A-3H</t>
+  </si>
+  <si>
+    <t>4D;UNASSIGNED_1, 4D-4A-4N-4G-1A-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4D-4O</t>
+  </si>
+  <si>
+    <t>4D;UNASSIGNED_1, 4D-4O</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4K-4F</t>
+  </si>
+  <si>
+    <t>4B;4W;UNASSIGNED_1, 4K-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4A-4P</t>
+  </si>
+  <si>
+    <t>4V;UNASSIGNED_1, 4V-4A-4P</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4G</t>
+  </si>
+  <si>
+    <t>4Q;4S;UNASSIGNED_1, 4V-4G</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4K</t>
+  </si>
+  <si>
+    <t>4Q;4V;UNASSIGNED_1, 4V-4K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4M</t>
+  </si>
+  <si>
+    <t>4Q;UNASSIGNED_1, 4V-4M</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4O</t>
+  </si>
+  <si>
+    <t>4Q;4V;UNASSIGNED_1, 4V-4O</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 5A-1C</t>
+  </si>
+  <si>
+    <t>5B;UNASSIGNED_1, 5A-1C</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6A-3A</t>
+  </si>
+  <si>
+    <t>6A;UNASSIGNED_1, 6A-3A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6A-3H</t>
+  </si>
+  <si>
+    <t>6A;UNASSIGNED_1, 6A-3H</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6G-3B</t>
+  </si>
+  <si>
+    <t>6G;UNASSIGNED_1, 6G-3B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
+  </si>
+  <si>
+    <t>6N;UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6P-2J-2A-2K-2J</t>
+  </si>
+  <si>
+    <t>2I;6P;UNASSIGNED_1, 6P-2J-2A-2K-2J</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6U-2B</t>
+  </si>
+  <si>
+    <t>6U;UNASSIGNED_1, 6U-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6W-2B</t>
+  </si>
+  <si>
+    <t>6W;UNASSIGNED_1, 6W-2B</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1A;1B;1C;1D;1G;1H;1I;1K;1L;1M;1N;1O;2K;5A;6B;6D;6P;6U;6W;6XA;6XD;6XG</t>
+  </si>
+  <si>
+    <t>1B;1C;1E;1N;1O</t>
+  </si>
+  <si>
+    <t>1A;1E</t>
+  </si>
+  <si>
+    <t>1D;1H</t>
+  </si>
+  <si>
+    <t>1L;4D</t>
+  </si>
+  <si>
+    <t>2A;2C;2D;2F;2I;2K;2L;2M;2P;2Q;2R;2U</t>
+  </si>
+  <si>
+    <t>2A;2B;2C;2D;2E;2I;2L;2Q;2T;7B</t>
+  </si>
+  <si>
+    <t>2B;2C;2F;2O</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>2B;2C;2D;2J;2L;2M;2Q;2T;3H;3I;5A;5B;6A;6G;6W;6XA;6XD;6XH;8A;UNASSIGNED_1, 2B-1B;UNASSIGNED_1, 2B-2D;UNASSIGNED_1, 3A-3G;UNASSIGNED_1, 5A-1C</t>
-  </si>
-  <si>
-    <t>2C</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1B;2C;2F;2J;2L;2Q;2R;UNASSIGNED_1, 2C-2B-3G-2B-2A;UNASSIGNED_1, 2C-6H-2B;UNASSIGNED_1, 2C-6H-3H</t>
-  </si>
-  <si>
-    <t>2D</t>
-  </si>
-  <si>
-    <t>2D;UNASSIGNED_1, 2D-2A</t>
-  </si>
-  <si>
-    <t>2I</t>
-  </si>
-  <si>
-    <t>2I;2K;UNASSIGNED_1, 2I-2K;UNASSIGNED_1, 2I-2K-2B-3H;UNASSIGNED_1, 2I-2K-2C-3H</t>
-  </si>
-  <si>
-    <t>2J</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>1G;2A;2C;2D;2E;2F;2I;2J;2K;2M;2Q;2R;2U;2V;3H;5A;7A;7B</t>
+  </si>
+  <si>
+    <t>2C;2F;2K;2Q;2U</t>
+  </si>
+  <si>
+    <t>2A;2K;2Q;2R;2U</t>
+  </si>
+  <si>
+    <t>1A;3A;3B;3D;3E;7B</t>
+  </si>
+  <si>
+    <t>3G;3I</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>3A;3H;3K</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>4A;4C;4E;4L;4N;4O;4P;4R;4V</t>
+  </si>
+  <si>
+    <t>1A;1D;4A;4B;4D;6F</t>
+  </si>
+  <si>
+    <t>4C;4D;4E;4F;4G;4V</t>
+  </si>
+  <si>
+    <t>1E;1G;1I;4A;4B;4D;4G;4H;4K;4L;4R;4V</t>
+  </si>
+  <si>
+    <t>4O</t>
+  </si>
+  <si>
+    <t>4O;4P;4V</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>1A;1B;1E;1K;4H;4K;4R;4V</t>
+  </si>
+  <si>
+    <t>4T</t>
+  </si>
+  <si>
+    <t>4P;4T</t>
+  </si>
+  <si>
+    <t>4A;4L;4M;4O;4P;4Q;4V</t>
+  </si>
+  <si>
+    <t>6A;6B;6XD;6XJ</t>
+  </si>
+  <si>
+    <t>1C;4V;5B;6C;6E;6EZ;6P;6Q;6XC;6XF;8A</t>
+  </si>
+  <si>
+    <t>5A;5B;6G</t>
+  </si>
+  <si>
+    <t>6J</t>
+  </si>
+  <si>
+    <t>4V;6K;6K-RELATED;6XB;6XI;8A</t>
+  </si>
+  <si>
+    <t>6K;6K-RELATED;6L;6L-RELATED;6XB;6XI;6XJ;8A</t>
+  </si>
+  <si>
+    <t>4C;4D;4V;5A;6N;6XE;6XG</t>
+  </si>
+  <si>
+    <t>4R;5A;6O;6Q;8A</t>
+  </si>
+  <si>
+    <t>6P</t>
+  </si>
+  <si>
+    <t>4Q;6P</t>
+  </si>
+  <si>
+    <t>1B;1D;5B;6Q</t>
+  </si>
+  <si>
+    <t>6T</t>
+  </si>
+  <si>
+    <t>1B;4R;6T</t>
+  </si>
+  <si>
+    <t>5A;6A;6G;6H;6L;6N;6Q;6T;6V;6W;6XA;6XC;6XD;6XE;6XF;6XG;6XH;8A</t>
+  </si>
+  <si>
+    <t>1D;5A;6U;6XA</t>
+  </si>
+  <si>
+    <t>1A;1I;1K;UNASSIGNED_1, 1A-1B</t>
+  </si>
+  <si>
+    <t>1A;UNASSIGNED_1, 1A-1C</t>
+  </si>
+  <si>
+    <t>1A;1B;1K;1N;1P;UNASSIGNED_1, 1B-1A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-2J-2A-2J-2K</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-2J-2A-2J-2K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1E-4A-4W-4F</t>
+  </si>
+  <si>
+    <t>1E;UNASSIGNED_1, 1E-4A-4W-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1E-4F-4W-4F-4P</t>
+  </si>
+  <si>
+    <t>1E;UNASSIGNED_1, 1E-4F-4W-4F-4P</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1H-4F</t>
+  </si>
+  <si>
+    <t>1H;UNASSIGNED_1, 1H-4F</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1L-1B-1A-4T-1A-4T</t>
+  </si>
+  <si>
+    <t>1L;UNASSIGNED_1, 1L-1B-1A-4T-1A-4T</t>
+  </si>
+  <si>
+    <t>2Q;UNASSIGNED_1, 2A-2K</t>
+  </si>
+  <si>
+    <t>2B;UNASSIGNED_1, 2B-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2B-2A</t>
+  </si>
+  <si>
+    <t>2A;2B;UNASSIGNED_1, 2B-2A</t>
+  </si>
+  <si>
+    <t>3H;UNASSIGNED_1, 3A-3G</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4A-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>4A;UNASSIGNED_1, 4A-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4A-6H-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>4A;UNASSIGNED_1, 4A-6H-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4R-4D</t>
+  </si>
+  <si>
+    <t>4D;4R;UNASSIGNED_1, 4R-4D</t>
+  </si>
+  <si>
+    <t>4Q;4S;4V;UNASSIGNED_1, 4V-4G</t>
+  </si>
+  <si>
+    <t>4Q;4S;4V;UNASSIGNED_1, 4V-4K</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 4V-4M-4P-4T-4A-3G-2B-1A-3H</t>
+  </si>
+  <si>
+    <t>4Q;4V;UNASSIGNED_1, 4V-4M-4P-4T-4A-3G-2B-1A-3H</t>
+  </si>
+  <si>
+    <t>4Q;UNASSIGNED_1, 4V-4O</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>1A;1B;1C;1D;1E;1G;1H;1J;1K;1L;1M;1N;1O;1P;2B;3A</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>1A;1B;1B-BASAL;1C;1D;1E;1G;1I;1K;1L;1M;1N;1O;2C;2K;3A;4F;6B;6D;6G;6N;6O;6P;6R;6XD;6XG</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
+    <t>1A;1C;1D;1I;1K;1L;1M;1O</t>
+  </si>
+  <si>
+    <t>1E;1L;1NC;4F</t>
+  </si>
+  <si>
+    <t>1B;1G</t>
+  </si>
+  <si>
+    <t>1D;1H;4F;5B</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>1A;1B;1C;1D;1E;1I;1J;1K;1L;1M;1N;1O;2NC;4F</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>2A;2B;2C;2D;2E;2F;2I;2K;2L;2M;2NC;2P;2Q;2R;2T;2U;2V</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2A;2B;2D;2F;2J;2K;2L;2NC;2Q;2R;2S;2T;2U;2V;3A;7B</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2A;2C;2D;2E;2F;2J;2K;2L;2O;2U;2V</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>533</t>
+  </si>
+  <si>
+    <t>589</t>
+  </si>
+  <si>
+    <t>2A;2B;2C;2D;2E;2F;2I;2J;2K;2L;2M;2NC;2P;2Q;2R;2T;2U;2V;3B;4F;5A;7A;7B;8A</t>
+  </si>
+  <si>
+    <t>2C;2E;2F;2I;2K;2Q;2R;2T;2U;2V</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>2A;2D;2K;2M;2NC;2R;2U;3M</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>2A;2B;2D;2F;2K;2L;2M;2Q;2R;2T;2U;2V</t>
+  </si>
+  <si>
+    <t>2R</t>
+  </si>
+  <si>
+    <t>2NC;2R;2U</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1A;1B;3A;3B;3D;3E;3I;6R;7B</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>2A;2F;3A;3B;3G;6XA</t>
+  </si>
+  <si>
+    <t>3E;3G;3H;3I;6XF</t>
+  </si>
+  <si>
+    <t>3A;3K</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1L;1M;4A;4C;4D;4E;4F;4G;4L;4M;4O;4P;4R;4S;4T;4V;4W</t>
+  </si>
+  <si>
+    <t>4C</t>
+  </si>
+  <si>
+    <t>4C;4K;4R</t>
+  </si>
+  <si>
+    <t>4A;4B;4C;4D;4L;4M;4O;4P;4S;4V;4W</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>1E;1H;1L;1N;2F;4A;4B;4C;4D;4E;4F;4K;4L;4M;4P;4R;4T;4V;4W;8A</t>
+  </si>
+  <si>
+    <t>4G</t>
+  </si>
+  <si>
+    <t>4G;4K;4W</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>1A;2L;2R;4B;4G;4H;4K;4L;4M;4P;4Q;4R;4V;6K;6R;8A</t>
+  </si>
+  <si>
+    <t>1M;4B;4C;4L;4M;4N;4S;4T;4V</t>
+  </si>
+  <si>
+    <t>1E;1M;2A;4C;4F;4L;4M;4P</t>
+  </si>
+  <si>
+    <t>4N</t>
+  </si>
+  <si>
+    <t>4F;4L;4N;4O</t>
+  </si>
+  <si>
+    <t>2R;4L;4O;4S;4W</t>
+  </si>
+  <si>
+    <t>4P</t>
+  </si>
+  <si>
+    <t>1E;4P;4T</t>
+  </si>
+  <si>
+    <t>4Q</t>
+  </si>
+  <si>
+    <t>4C;4L;4M;4P;4R;4V</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>1L;4A;4B;4C;4D;4E;4F;4G;4K;4L;4M;4N;4NC;4P;4Q;4R;4S;4T;4U;4V;4W</t>
+  </si>
+  <si>
+    <t>4B;4W;8A</t>
+  </si>
+  <si>
+    <t>1A;5A</t>
+  </si>
+  <si>
+    <t>6A;6B;6D;6J;6N;6P;6XD</t>
+  </si>
+  <si>
+    <t>6B</t>
+  </si>
+  <si>
+    <t>6B;6XD</t>
+  </si>
+  <si>
+    <t>1H;6C;6F</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>1A;1C;1D;1G;1L;1N;3D;6C;6D;6E;6F;6P;6Q;6T;6U;6X;6XA;6XC;6XF;6XH;7A;7B;8A</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
+    <t>1B;6F;6Q;6R;6XF;7A;8A</t>
+  </si>
+  <si>
+    <t>1M;1N;3D;6G;6O;6R;6XF;7B;8A</t>
+  </si>
+  <si>
+    <t>1L;1M;2L;3D;3G;6H;8A</t>
+  </si>
+  <si>
+    <t>6I</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>1A;1D;1L;1M;6I;6P;7A;8A</t>
+  </si>
+  <si>
     <t>43</t>
   </si>
   <si>
-    <t>1K;2A;2B;2C;2D;2E;2F;2I;2J;2K;2M;2Q;2R;2T;2U;2V;6E;6Q;7B;UNASSIGNED_1, 2J-6K</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>2A;2D;2J;2K;2M;2Q;2R</t>
-  </si>
-  <si>
-    <t>2M</t>
-  </si>
-  <si>
-    <t>2J;2M;2Q</t>
-  </si>
-  <si>
-    <t>2Q</t>
-  </si>
-  <si>
-    <t>2A;2J;2K;2M;2Q</t>
-  </si>
-  <si>
-    <t>3A</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>1A;1B;2J;3A;3D;3E;UNASSIGNED_1, 3A-2B;UNASSIGNED_1, 3A-3H</t>
-  </si>
-  <si>
-    <t>3B</t>
-  </si>
-  <si>
-    <t>3B;3G;3I;UNASSIGNED_1, 3B-3A;UNASSIGNED_1, 3B-3H</t>
-  </si>
-  <si>
-    <t>3H</t>
-  </si>
-  <si>
-    <t>1K;3H;8A;UNASSIGNED_1, 3H-6A</t>
-  </si>
-  <si>
-    <t>3I</t>
-  </si>
-  <si>
-    <t>3I;UNASSIGNED_1, 3I-3H-6H-6B;UNASSIGNED_1, 3I-3K</t>
-  </si>
-  <si>
-    <t>4A</t>
-  </si>
-  <si>
-    <t>4A;4B;4C;4E;4F;4K;4O;4P;UNASSIGNED_1, 4A-1A</t>
-  </si>
-  <si>
-    <t>4D</t>
-  </si>
-  <si>
-    <t>4A;4D;UNASSIGNED_1, 4D-4A-4N-4G-1A-3H;UNASSIGNED_1, 4D-4O</t>
-  </si>
-  <si>
-    <t>4F</t>
-  </si>
-  <si>
-    <t>4F;4Q;4S;4V;6L;6W;6XD;UNASSIGNED_1, 4V-4G</t>
-  </si>
-  <si>
-    <t>4G?</t>
-  </si>
-  <si>
-    <t>4G;4G?</t>
-  </si>
-  <si>
-    <t>4K</t>
-  </si>
-  <si>
-    <t>4B;4G;4H;4K;4R;4W;6Q;UNASSIGNED_1, 4K-4F</t>
-  </si>
-  <si>
-    <t>4L</t>
-  </si>
-  <si>
-    <t>4A;4L;4V</t>
-  </si>
-  <si>
-    <t>4M</t>
-  </si>
-  <si>
-    <t>1B;4M</t>
-  </si>
-  <si>
-    <t>4R</t>
-  </si>
-  <si>
-    <t>4A;4R</t>
-  </si>
-  <si>
-    <t>4V</t>
-  </si>
-  <si>
-    <t>2L;4B;4Q;4V;UNASSIGNED_1, 4V-4A-4P;UNASSIGNED_1, 4V-4G;UNASSIGNED_1, 4V-4K;UNASSIGNED_1, 4V-4M;UNASSIGNED_1, 4V-4O</t>
-  </si>
-  <si>
-    <t>4W</t>
-  </si>
-  <si>
-    <t>4B;4W</t>
-  </si>
-  <si>
-    <t>5A</t>
-  </si>
-  <si>
-    <t>2L;5A</t>
-  </si>
-  <si>
-    <t>6A</t>
-  </si>
-  <si>
-    <t>6A;6B;6G;6XD;UNASSIGNED_1, 6A-3A;UNASSIGNED_1, 6A-3H</t>
-  </si>
-  <si>
-    <t>6C</t>
-  </si>
-  <si>
-    <t>1H;6C</t>
-  </si>
-  <si>
-    <t>6D</t>
-  </si>
-  <si>
-    <t>1H;6D;8A</t>
-  </si>
-  <si>
-    <t>6E</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1B;1C;6C;6E;6EZ;6Q;6U;6W;6XC;6XF</t>
-  </si>
-  <si>
-    <t>6L</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>1A;6K;6K-RELATED;6L;6L-RELATED;6XB;6XI;6XJ;8A</t>
-  </si>
-  <si>
-    <t>6M</t>
-  </si>
-  <si>
-    <t>6M;8A</t>
-  </si>
-  <si>
-    <t>6N</t>
-  </si>
-  <si>
-    <t>6N;6XE;6XG;UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
-  </si>
-  <si>
-    <t>6O</t>
-  </si>
-  <si>
-    <t>6C;6E</t>
-  </si>
-  <si>
-    <t>6P</t>
-  </si>
-  <si>
-    <t>2I;6P;UNASSIGNED_1, 6P-2J-2A-2K-2J</t>
-  </si>
-  <si>
-    <t>6Q</t>
-  </si>
-  <si>
-    <t>1A;6Q</t>
-  </si>
-  <si>
-    <t>6R</t>
-  </si>
-  <si>
-    <t>1K;6R</t>
-  </si>
-  <si>
-    <t>6S</t>
-  </si>
-  <si>
-    <t>1J;6S</t>
-  </si>
-  <si>
-    <t>6T</t>
-  </si>
-  <si>
-    <t>6E;6O;6Q</t>
+    <t>51</t>
+  </si>
+  <si>
+    <t>1A;1L;1M;2A;3G;3H;3I;4K;6J;7A;8A</t>
+  </si>
+  <si>
+    <t>1C;1J;6K;6K-RELATED;6XI;8A</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1A;1C;1L;1M;1N;2A;2M;6H;6K;6K-RELATED;6L;6L-RELATED;6XB;6XF;6XI;6XJ;8A</t>
+  </si>
+  <si>
+    <t>1A;1C;1G;1L;1M;1N;6N;6X;6XE;6XG;8A</t>
+  </si>
+  <si>
+    <t>1D;6O;6P;6Q</t>
+  </si>
+  <si>
+    <t>3D;6P;8A</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>2U;3B;3D;3E;6Q;7A;8A</t>
+  </si>
+  <si>
+    <t>1D;1E;1K;1M;3K;6R;8A</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>1A;1E;1J;6S</t>
+  </si>
+  <si>
+    <t>1A;4D;4W;6C;6F;6O;6P;6Q;6T;6XF;7A;8A</t>
   </si>
   <si>
     <t>6U</t>
   </si>
   <si>
-    <t>6U;UNASSIGNED_1, 6U-2B</t>
-  </si>
-  <si>
-    <t>6W</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>2L;2T;6E;6G;6H;6L;6Q;6S;6W;6XA;6XF;6XH;6XJ;8A;UNASSIGNED_1, 6W-2B</t>
-  </si>
-  <si>
-    <t>6XA</t>
-  </si>
-  <si>
-    <t>6U;6XA</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1A-1B</t>
-  </si>
-  <si>
-    <t>1A;UNASSIGNED_1, 1A-1B</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1A-4A</t>
-  </si>
-  <si>
-    <t>1A;UNASSIGNED_1, 1A-4A-4V</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1A-4D</t>
-  </si>
-  <si>
-    <t>1A;UNASSIGNED_1, 1A-4D</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1B-4A</t>
-  </si>
-  <si>
-    <t>1A;1P;UNASSIGNED_1, 1A-4A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1L-1A</t>
-  </si>
-  <si>
-    <t>1A;1L;UNASSIGNED_1, 1A-1L</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 3A-1A</t>
-  </si>
-  <si>
-    <t>3A;UNASSIGNED_1, 3A-1A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 3A-2B</t>
-  </si>
-  <si>
-    <t>3A;UNASSIGNED_1, 3A-2B</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 4A-1A</t>
-  </si>
-  <si>
-    <t>4A;UNASSIGNED_1, 4A-1A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 4V-4K</t>
-  </si>
-  <si>
-    <t>4Q;UNASSIGNED_1, 4V-4K</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1J;1K;1L;1M;1N;1O;1P;2B;3A;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1A-1C;UNASSIGNED_1, 1A-1L;UNASSIGNED_1, 1A-2B;UNASSIGNED_1, 1A-3A;UNASSIGNED_1, 1A-4A;UNASSIGNED_1, 1B-1A</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1G;1H;1I;1K;1L;1M;1N;1O;1P;2B;2K;2K1B;5A;6A;6B;6G;6H;6Q;6T;6V;6W;6XA;6XE;6XF;6XG;6XJ;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1B-1A;UNASSIGNED_1, 1B-2A;UNASSIGNED_1, 1B-2A-2K;UNASSIGNED_1, 1B-2B;UNASSIGNED_1, 1B-2B-6D-6B;UNASSIGNED_1, 1B-2J-2A-2B;UNASSIGNED_1, 1B-2J-2A-2J-2K;UNASSIGNED_1, 1B-2J-2A-2J-2Q-2K-2Q-2K;UNASSIGNED_1, 1B-2J-2K;UNASSIGNED_1, 1B-2J-2Q-2K;UNASSIGNED_1, 1B-2K;UNASSIGNED_1, 1B-3H;UNASSIGNED_1, 1B-6B;UNASSIGNED_1, 1B-6H-2A-6H-6D-3G;UNASSIGNED_1, 1B-6H-6B;UNASSIGNED_1, 1B-6K-6B;UNASSIGNED_1, 1B-6K-6D-6B</t>
-  </si>
-  <si>
-    <t>1B;1C;1E;1N;1O</t>
-  </si>
-  <si>
-    <t>1A;1E;UNASSIGNED_1, 1E-4A-4W-4F;UNASSIGNED_1, 1E-4F-4W-4F-4P;UNASSIGNED_1, 1E-4K-4N-4G-4A-4F-4D-4G</t>
-  </si>
-  <si>
-    <t>1D;1H;UNASSIGNED_1, 1H-4F;UNASSIGNED_1, 1H-4F-4L-4F</t>
-  </si>
-  <si>
-    <t>1L;4D;6G;6Q;6W;6XG;UNASSIGNED_1, 1L-1A;UNASSIGNED_1, 1L-1A-1B;UNASSIGNED_1, 1L-1B-1A-4T-1A-4T;UNASSIGNED_1, 1L-2A;UNASSIGNED_1, 1L-2K-2A;UNASSIGNED_1, 1L-2K-2J-2A-2Q;UNASSIGNED_1, 1L-4F;UNASSIGNED_1, 1L-4V-4F</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>2A;2B;2C;2D;2F;2I;2J;2K;2L;2M;2P;2Q;2R;2U;2V;UNASSIGNED_1, 2A-3A</t>
-  </si>
-  <si>
-    <t>1B;2A;2B;2C;2D;2E;2I;2L;2Q;2T;6B;6D;UNASSIGNED_1, 2B-1B</t>
-  </si>
-  <si>
-    <t>2B;2C;2D;2F;2J;2O;2Q;UNASSIGNED_1, 2C-2B-3G-2B-2A;UNASSIGNED_1, 2C-6H-2B;UNASSIGNED_1, 2C-6H-3H</t>
-  </si>
-  <si>
-    <t>2I;UNASSIGNED_1, 2I-2K;UNASSIGNED_1, 2I-2K-2B-3H;UNASSIGNED_1, 2I-2K-2C-3H</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>2A;2B;2C;2D;2E;2F;2I;2J;2K;2L;2M;2Q;2R;2U;2V;3H;6W;7A;8A;UNASSIGNED_1, 2J-5A;UNASSIGNED_1, 2J-6K</t>
-  </si>
-  <si>
-    <t>2C;2F;2K;2Q;2U</t>
-  </si>
-  <si>
-    <t>2A;2C;2J;2K;2Q;2R;2U;UNASSIGNED_1, 2A-2K</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>1A;2B;3A;3B;3D;3E;6N;6W;6XA;7B;8A;UNASSIGNED_1, 2J-5A;UNASSIGNED_1, 3A-1A;UNASSIGNED_1, 3A-2B;UNASSIGNED_1, 3A-3H</t>
-  </si>
-  <si>
-    <t>3B;3H;UNASSIGNED_1, 3A-3G;UNASSIGNED_1, 3B-3A;UNASSIGNED_1, 3B-3H</t>
-  </si>
-  <si>
-    <t>3G</t>
-  </si>
-  <si>
-    <t>3G;3I</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>4A;4B;4C;4K;4L;4N;4O;4P;4R;4V;6E;6P;8A;UNASSIGNED_1, 1B-6W;UNASSIGNED_1, 4A-6B-6H-6B;UNASSIGNED_1, 4A-6H-6B-6H-6B</t>
-  </si>
-  <si>
-    <t>4C</t>
-  </si>
-  <si>
-    <t>4A;4C</t>
-  </si>
-  <si>
-    <t>1A;1D;4A;4B;4D;4K;6F;UNASSIGNED_1, 4D-4A-4N-4G-1A-3H;UNASSIGNED_1, 4D-4O</t>
-  </si>
-  <si>
-    <t>4D;4F;4G</t>
-  </si>
-  <si>
-    <t>4G</t>
-  </si>
-  <si>
-    <t>4G;4H;4K</t>
-  </si>
-  <si>
-    <t>1B;1E;1G;1H;1I;2J;4A;4D;4G;4H;4K;4L;4R;6A;6D;6G;6L;6W;6XA;6XD;6XJ;7A;7B</t>
-  </si>
-  <si>
-    <t>4S;5A;6W;8A;UNASSIGNED_1, 4V-4G</t>
-  </si>
-  <si>
-    <t>4O</t>
-  </si>
-  <si>
-    <t>3A;3H;3K;4O;4P;4V</t>
-  </si>
-  <si>
-    <t>4Q</t>
-  </si>
-  <si>
-    <t>4Q;4S;4V;UNASSIGNED_1, 4V-4K</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>1A;1B;1E;1K;4H;4K;4R;4V;6E;6XF</t>
-  </si>
-  <si>
-    <t>4T</t>
-  </si>
-  <si>
-    <t>4P;4T</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>1G;2J;4A;4B;4C;4E;4F;4G;4K;4L;4M;4O;4P;4Q;4S;4V;4W;7B;UNASSIGNED_1, 4K-4F;UNASSIGNED_1, 4V-4A-4P;UNASSIGNED_1, 4V-4G;UNASSIGNED_1, 4V-4K;UNASSIGNED_1, 4V-4M;UNASSIGNED_1, 4V-4M-4P-4T-4A-3G-2B-1A-3H;UNASSIGNED_1, 4V-4O</t>
-  </si>
-  <si>
-    <t>5B;UNASSIGNED_1, 5A-1C</t>
-  </si>
-  <si>
-    <t>1C;1K;3H;6A;6B;6E;6Q;6XC;6XD;UNASSIGNED_1, 3H-6A</t>
-  </si>
-  <si>
-    <t>6D;8A</t>
-  </si>
-  <si>
-    <t>4V;5B;6E;6EZ;6XC</t>
-  </si>
-  <si>
-    <t>6G</t>
-  </si>
-  <si>
-    <t>5B;6G;UNASSIGNED_1, 6G-3B</t>
-  </si>
-  <si>
-    <t>6I</t>
-  </si>
-  <si>
-    <t>6J</t>
-  </si>
-  <si>
-    <t>6K</t>
-  </si>
-  <si>
-    <t>4V;6K;6K-RELATED;6L;6XB;6XI;6XJ;8A</t>
-  </si>
-  <si>
-    <t>6K;6K-RELATED;6L;6L-RELATED;6XB;6XI;6XJ;8A</t>
-  </si>
-  <si>
-    <t>4C;4D;4V;5A;6N;6XE;6XG;UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
-  </si>
-  <si>
-    <t>4R;5A;6C;6E;6K;6K-RELATED;6L;6O;6Q;6XB;8A</t>
-  </si>
-  <si>
-    <t>2I;4Q;6P;UNASSIGNED_1, 6P-2J-2A-2K-2J</t>
-  </si>
-  <si>
-    <t>1B;1D;5B;6E;6Q</t>
-  </si>
-  <si>
-    <t>1B;4R;6E;6G;6Q;6T;6W</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>1B;2J;5A;6G;6L;6O;6P;6Q;6U;6W;6XA;6XC;6XE;6XF;6XH;8A;UNASSIGNED_1, 6W-2B</t>
-  </si>
-  <si>
-    <t>1D;5A;6U;6XA</t>
-  </si>
-  <si>
-    <t>1A;1I;UNASSIGNED_1, 1A-1B</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1B-1A</t>
-  </si>
-  <si>
-    <t>1A;1B;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1B-1A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 2B-2A</t>
-  </si>
-  <si>
-    <t>2A;2B;UNASSIGNED_1, 2B-2A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 4R-4D</t>
-  </si>
-  <si>
-    <t>4D;4R;UNASSIGNED_1, 4R-4D</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1E;1G;1H;1J;1K;1L;1M;1N;1O;2B;3A;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1A-2B;UNASSIGNED_1, 1A-3A</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>1A;1B;1B-BASAL;1C;1D;1E;1G;1H;1I;1K;1L;1M;1N;1O;1P;2B;2C;2K;2K1B;3A;4F;6B;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1B-1A;UNASSIGNED_1, 1B-2A-2K;UNASSIGNED_1, 1B-2B;UNASSIGNED_1, 1B-2B-6D-6B;UNASSIGNED_1, 1B-2J-2A-2B;UNASSIGNED_1, 1B-2J-2A-2J-2Q-2K-2Q-2K;UNASSIGNED_1, 1B-2J-2K;UNASSIGNED_1, 1B-2J-2Q-2K;UNASSIGNED_1, 1B-2K;UNASSIGNED_1, 1B-3A;UNASSIGNED_1, 1B-3H;UNASSIGNED_1, 1B-6B;UNASSIGNED_1, 1B-6B-6H-6B;UNASSIGNED_1, 1B-6D-6B;UNASSIGNED_1, 1B-6H-2A-6H-6D-3G;UNASSIGNED_1, 1B-6H-6B;UNASSIGNED_1, 1B-6H-6D;UNASSIGNED_1, 1B-6K-6B;UNASSIGNED_1, 1B-6K-6D-6B</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1I;1K;1L;1M;1O;4D;UNASSIGNED_1, 1A-1C</t>
-  </si>
-  <si>
-    <t>1E;1L;1NC;4F;UNASSIGNED_1, 1E-4A-4W-4F;UNASSIGNED_1, 1E-4F-4W-4F-4P;UNASSIGNED_1, 1E-4K-4N-4G-4A-4F-4D-4G</t>
-  </si>
-  <si>
-    <t>1B;1G</t>
-  </si>
-  <si>
-    <t>1B;1D;1H;4F;5B;UNASSIGNED_1, 1H-4F;UNASSIGNED_1, 1H-4F-4L-4F</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1E;1I;1J;1K;1L;1M;1N;1O;2NC;4F;UNASSIGNED_1, 1A-1L;UNASSIGNED_1, 1L-1A;UNASSIGNED_1, 1L-1A-1B;UNASSIGNED_1, 1L-2A;UNASSIGNED_1, 1L-2K-2A;UNASSIGNED_1, 1L-2K-2J-2A-2Q;UNASSIGNED_1, 1L-4F;UNASSIGNED_1, 1L-4V-4F</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>2A;2B;2C;2D;2E;2F;2I;2J;2K;2L;2M;2NC;2P;2Q;2R;2T;2U;2V;UNASSIGNED_1, 2A-1B;UNASSIGNED_1, 2A-2B;UNASSIGNED_1, 2A-2C;UNASSIGNED_1, 2A-3A</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>2A;2B;2C;2D;2F;2J;2K;2L;2M;2NC;2Q;2R;2S;2T;2U;2V;3A;7B;8A;UNASSIGNED_1, 1B-6W;UNASSIGNED_1, 2B-1B</t>
-  </si>
-  <si>
-    <t>1A;2A;2C;2D;2E;2F;2J;2K;2L;2O;2Q;2R;2U;2V;UNASSIGNED_1, 2C-2B-3G-2B-2A;UNASSIGNED_1, 2C-6H-2B;UNASSIGNED_1, 2C-6H-3H</t>
-  </si>
-  <si>
-    <t>2I;2J;UNASSIGNED_1, 2I-2K;UNASSIGNED_1, 2I-2K-2B-3H;UNASSIGNED_1, 2I-2K-2C-3H</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>496</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>2A;2B;2C;2D;2E;2F;2I;2J;2K;2L;2M;2NC;2P;2Q;2R;2T;2U;2V;4F;7A;8A;UNASSIGNED_1, 2J-6K</t>
-  </si>
-  <si>
-    <t>2A;2C;2D;2E;2F;2I;2J;2K;2M;2Q;2R;2U;2V</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>2A;2D;2J;2K;2M;2NC;2R;2U;3M</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>2A;2B;2D;2F;2J;2K;2L;2M;2Q;2R;2T;2U;2V</t>
-  </si>
-  <si>
-    <t>2R</t>
-  </si>
-  <si>
-    <t>2NC;2R;2U</t>
-  </si>
-  <si>
-    <t>63</t>
+    <t>6E;6U</t>
+  </si>
+  <si>
+    <t>6V</t>
+  </si>
+  <si>
+    <t>2U;3D;6V</t>
   </si>
   <si>
     <t>85</t>
   </si>
   <si>
-    <t>1A;1B;3A;3B;3D;3E;3H;3I;6R;6W;7B;8A;UNASSIGNED_1, 3A-1A;UNASSIGNED_1, 3A-2B;UNASSIGNED_1, 3A-3G;UNASSIGNED_1, 3A-3H;UNASSIGNED_1, 3B-3A</t>
-  </si>
-  <si>
-    <t>2A;2F;2J;3A;3B;3G;6XA;UNASSIGNED_1, 3B-3H</t>
-  </si>
-  <si>
-    <t>3E;3G;3H;3I;6XF</t>
-  </si>
-  <si>
-    <t>1K;3H;UNASSIGNED_1, 3H-6A</t>
-  </si>
-  <si>
-    <t>3I;UNASSIGNED_1, 3I-3H-6H-6B</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>3A;3K</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1L;1M;2J;4A;4C;4D;4E;4F;4G;4L;4M;4O;4P;4Q;4R;4S;4T;4V;4W;7B;UNASSIGNED_1, 4A-1A</t>
-  </si>
-  <si>
-    <t>4C;4K;4R</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>4A;4B;4C;4D;4L;4M;4O;4P;4S;4V;4W;UNASSIGNED_1, 4D-4O</t>
-  </si>
-  <si>
-    <t>1E;1H;1L;1N;2F;4A;4B;4C;4D;4E;4F;4K;4L;4M;4P;4R;4T;4V;4W;8A</t>
-  </si>
-  <si>
-    <t>4G;4K;4W</t>
-  </si>
-  <si>
-    <t>1A;1B;2L;2R;4B;4G;4H;4K;4L;4M;4P;4Q;4R;4V;4W;6K;6R;6XD;8A;UNASSIGNED_1, 4K-4F</t>
-  </si>
-  <si>
-    <t>1M;4B;4C;4L;4M;4N;4S;4T;4V</t>
-  </si>
-  <si>
-    <t>1E;1M;2A;4C;4F;4L;4M;4P;4R</t>
-  </si>
-  <si>
-    <t>4N</t>
-  </si>
-  <si>
-    <t>4C;4F;4L;4N;4O;4V</t>
-  </si>
-  <si>
-    <t>2R;4A;4L;4O;4S;4W</t>
-  </si>
-  <si>
-    <t>4P</t>
-  </si>
-  <si>
-    <t>1E;4D;4M;4P;4T</t>
-  </si>
-  <si>
-    <t>4C;4L;4P;4R;4V</t>
-  </si>
-  <si>
-    <t>4T;4V</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>1L;4A;4B;4C;4D;4E;4F;4G;4K;4L;4M;4N;4NC;4P;4Q;4R;4S;4T;4U;4V;4W;6Q;6T;8A;UNASSIGNED_1, 4V-4A-4P;UNASSIGNED_1, 4V-4G;UNASSIGNED_1, 4V-4K;UNASSIGNED_1, 4V-4M;UNASSIGNED_1, 4V-4M-4P-4T-4A-3G-2B-1A-3H;UNASSIGNED_1, 4V-4O</t>
-  </si>
-  <si>
-    <t>4B;4W;8A</t>
-  </si>
-  <si>
-    <t>1A;2J;5A;5B;UNASSIGNED_1, 5A-1C</t>
-  </si>
-  <si>
-    <t>2J;5A;6A;6B;6D;6J;6N;6R;6W;6XA;6XD;6XG;7A;8A;UNASSIGNED_1, 2J-5A;UNASSIGNED_1, 6A-1B;UNASSIGNED_1, 6A-3A;UNASSIGNED_1, 6A-3H</t>
-  </si>
-  <si>
-    <t>6B</t>
-  </si>
-  <si>
-    <t>6B;6XD</t>
-  </si>
-  <si>
-    <t>1H;6C;6F</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1D;1G;1L;1N;3D;6A;6B;6C;6D;6E;6F;6N;6O;6P;6Q;6T;6U;6W;6X;6XA;6XC;6XF;6XG;6XH;7A;7B;8A</t>
-  </si>
-  <si>
-    <t>6F</t>
-  </si>
-  <si>
-    <t>1B;6C;6F;6Q;6R;6T;6XF;7A;8A</t>
-  </si>
-  <si>
-    <t>1B;1M;1N;3D;6D;6G;6O;6R;6W;6XF;7B;8A;UNASSIGNED_1, 6G-3B</t>
-  </si>
-  <si>
-    <t>6H</t>
-  </si>
-  <si>
-    <t>1L;1M;2L;3D;3G;6H;8A</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>1A;1D;1L;1M;6I;6P;7A;8A</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>1A;1L;1M;2A;3G;3H;3I;4K;6J;7A;8A</t>
-  </si>
-  <si>
-    <t>1C;1J;6K;6L;6XI;6XJ;8A</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>1A;1C;1L;1M;1N;2A;2M;6H;6K;6K-RELATED;6L;6L-RELATED;6XB;6XF;6XI;6XJ;8A</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>1A;1C;1G;1L;1M;1N;6H;6I;6L;6N;6W;6X;6XE;6XG;6XJ;8A</t>
-  </si>
-  <si>
-    <t>1B;1D;6O;6P;6W;6XF</t>
-  </si>
-  <si>
-    <t>2I;3D;6P;8A;UNASSIGNED_1, 6P-2J-2A-2K-2J</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>2U;3B;3D;3E;6Q;7A;8A</t>
-  </si>
-  <si>
-    <t>1D;1E;1K;1M;3K;6R;8A</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>1A;1E;1J;6S</t>
-  </si>
-  <si>
-    <t>1A;4D;4W;6F;6O;6P;6T;6XF;7A;8A</t>
-  </si>
-  <si>
-    <t>6E;6U;UNASSIGNED_1, 6U-2B</t>
-  </si>
-  <si>
-    <t>6V</t>
-  </si>
-  <si>
-    <t>2U;3D;6V</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>1A;1M;1N;6E;6G;6L;6N;6P;6R;6T;6W;6XA;6XD;6XF;6XG;6XH;7A;7B;8A;UNASSIGNED_1, 2J-5A;UNASSIGNED_1, 6W-2B</t>
-  </si>
-  <si>
-    <t>1A;UNASSIGNED_1, 1A-4A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1A-4A-4V</t>
-  </si>
-  <si>
-    <t>1A;1B;1C;1P;UNASSIGNED_1, 1A-1B;UNASSIGNED_1, 1A-4A;UNASSIGNED_1, 1B-1A</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 1B-2A</t>
+    <t>1A;1M;1N;5A;6C;6G;6H;6I;6L;6N;6P;6Q;6R;6T;6W;6XA;6XD;6XF;6XG;6XH;7A;7B;8A</t>
+  </si>
+  <si>
+    <t>1A;1B;1D;1K;UNASSIGNED_1, 1A-1B</t>
+  </si>
+  <si>
+    <t>1A;1B;1D;1H;1P;UNASSIGNED_1, 1B-1A</t>
   </si>
   <si>
     <t>1D;1I;UNASSIGNED_1, 1B-2A</t>
   </si>
   <si>
-    <t>UNASSIGNED_1, 1C-1B</t>
-  </si>
-  <si>
-    <t>1A;1O</t>
-  </si>
-  <si>
-    <t>UNASSIGNED_1, 2A-2K</t>
+    <t>UNASSIGNED_1, 1B-3A</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-3A</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6B-6H-6B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 1B-6H-6D</t>
+  </si>
+  <si>
+    <t>1B;UNASSIGNED_1, 1B-6H-6D</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2A-1B</t>
+  </si>
+  <si>
+    <t>2A;UNASSIGNED_1, 2A-1B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2A-2B</t>
+  </si>
+  <si>
+    <t>2A;2B;UNASSIGNED_1, 2A-2B</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 2A-2C</t>
+  </si>
+  <si>
+    <t>2A;2C;UNASSIGNED_1, 2A-2C</t>
   </si>
   <si>
     <t>2K;2Q;UNASSIGNED_1, 2A-2K</t>
@@ -1046,22 +1448,28 @@
     <t>2A;6W;UNASSIGNED_1, 2A-6V</t>
   </si>
   <si>
-    <t>UNASSIGNED_1, 2B-1A</t>
-  </si>
-  <si>
-    <t>1A;UNASSIGNED_1, 1A-2B</t>
-  </si>
-  <si>
     <t>UNASSIGNED_1, 3A-6H</t>
   </si>
   <si>
     <t>3A;UNASSIGNED_1, 3A-6H</t>
   </si>
   <si>
-    <t>UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
-  </si>
-  <si>
-    <t>6N;UNASSIGNED_1, 6N-6O-6E-6A-6O</t>
+    <t>3A;3B;UNASSIGNED_1, 3B-3A</t>
+  </si>
+  <si>
+    <t>4L;4Q;4S;UNASSIGNED_1, 4V-4G</t>
+  </si>
+  <si>
+    <t>4Q;4V;UNASSIGNED_1, 4V-4M</t>
+  </si>
+  <si>
+    <t>4L;4Q;UNASSIGNED_1, 4V-4O</t>
+  </si>
+  <si>
+    <t>UNASSIGNED_1, 6A-1B</t>
+  </si>
+  <si>
+    <t>6A;UNASSIGNED_1, 6A-1B</t>
   </si>
 </sst>
 </file>
@@ -1408,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -1477,616 +1885,616 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
@@ -2095,236 +2503,236 @@
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
         <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="E50" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
@@ -2333,58 +2741,1163 @@
         <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" t="s">
+        <v>140</v>
+      </c>
+      <c r="E58" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
         <v>145</v>
       </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" t="s">
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>146</v>
+      </c>
+      <c r="B61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>150</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>152</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" t="s">
+        <v>68</v>
+      </c>
+      <c r="E64" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>160</v>
+      </c>
+      <c r="B68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>162</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>168</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>172</v>
+      </c>
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>186</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>188</v>
+      </c>
+      <c r="B82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>190</v>
+      </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>192</v>
+      </c>
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>196</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>198</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>202</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>204</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>206</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>68</v>
+      </c>
+      <c r="E94" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>216</v>
+      </c>
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>218</v>
+      </c>
+      <c r="B97" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>220</v>
+      </c>
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>34</v>
+      </c>
+      <c r="E98" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>222</v>
+      </c>
+      <c r="B99" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" t="s">
+        <v>225</v>
+      </c>
+      <c r="D100" t="s">
+        <v>225</v>
+      </c>
+      <c r="E100" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>229</v>
+      </c>
+      <c r="B102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>235</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>68</v>
+      </c>
+      <c r="E111" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" t="s">
+        <v>21</v>
+      </c>
+      <c r="C114" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>257</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>259</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>267</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2395,7 +3908,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -2427,16 +3940,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>272</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2444,16 +3957,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>273</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2461,135 +3974,135 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>157</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>160</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>162</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2600,13 +4113,13 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2614,237 +4127,237 @@
         <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
         <v>68</v>
       </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
-        <v>28</v>
-      </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>176</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>298</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>183</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2852,228 +4365,228 @@
         <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>272</v>
       </c>
       <c r="E30" t="s">
-        <v>191</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>195</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
       <c r="C34" t="s">
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>196</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>197</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>95</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>199</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>201</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
@@ -3082,296 +4595,1401 @@
         <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>106</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>48</v>
+        <v>272</v>
       </c>
       <c r="D44" t="s">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>319</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>209</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>210</v>
+        <v>321</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="E52" t="s">
-        <v>214</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>215</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E54" t="s">
-        <v>216</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>220</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>323</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>162</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>166</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>168</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>170</v>
+      </c>
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>325</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>327</v>
+      </c>
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>329</v>
+      </c>
+      <c r="B73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>331</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>186</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>188</v>
+      </c>
+      <c r="B82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>190</v>
+      </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>192</v>
+      </c>
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>194</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>335</v>
+      </c>
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>198</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>16</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>202</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>204</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>206</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>208</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>68</v>
+      </c>
+      <c r="E94" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>218</v>
+      </c>
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>220</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" t="s">
         <v>221</v>
       </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" t="s">
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
         <v>222</v>
+      </c>
+      <c r="B98" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>224</v>
+      </c>
+      <c r="B99" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" t="s">
+        <v>225</v>
+      </c>
+      <c r="D99" t="s">
+        <v>225</v>
+      </c>
+      <c r="E99" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>227</v>
+      </c>
+      <c r="B100" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>229</v>
+      </c>
+      <c r="B101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>231</v>
+      </c>
+      <c r="B102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>233</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>235</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>338</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>340</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>342</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="s">
+        <v>21</v>
+      </c>
+      <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>245</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>247</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" t="s">
+        <v>68</v>
+      </c>
+      <c r="E112" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>249</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>251</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>346</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>253</v>
+      </c>
+      <c r="B116" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>255</v>
+      </c>
+      <c r="B117" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>261</v>
+      </c>
+      <c r="B118" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>263</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>265</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>267</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -3382,7 +6000,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -3414,16 +6032,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>349</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>350</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
-        <v>226</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3431,16 +6049,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>229</v>
+        <v>355</v>
       </c>
       <c r="E3" t="s">
-        <v>230</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3448,152 +6066,152 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="E4" t="s">
-        <v>233</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>235</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>363</v>
       </c>
       <c r="D8" t="s">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="E8" t="s">
-        <v>239</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>241</v>
+        <v>366</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>369</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="D10" t="s">
-        <v>246</v>
+        <v>370</v>
       </c>
       <c r="E10" t="s">
-        <v>247</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="E11" t="s">
-        <v>248</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>374</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>375</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>376</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3601,976 +6219,976 @@
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>249</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>379</v>
       </c>
       <c r="B14" t="s">
-        <v>250</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
       <c r="D14" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="E14" t="s">
-        <v>253</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>382</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>383</v>
       </c>
       <c r="E15" t="s">
-        <v>254</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>385</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>232</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>256</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>257</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>176</v>
+        <v>387</v>
       </c>
       <c r="E17" t="s">
-        <v>258</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>259</v>
+        <v>389</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>260</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>261</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>262</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>263</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>290</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>273</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>393</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>394</v>
       </c>
       <c r="E21" t="s">
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>266</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>369</v>
       </c>
       <c r="E23" t="s">
-        <v>267</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>268</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>399</v>
       </c>
       <c r="E24" t="s">
-        <v>269</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>401</v>
       </c>
       <c r="B25" t="s">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>271</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>272</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>273</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>274</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>275</v>
+        <v>403</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
         <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>372</v>
       </c>
       <c r="E28" t="s">
-        <v>277</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>182</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>282</v>
       </c>
       <c r="E29" t="s">
-        <v>278</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>407</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>408</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>279</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>280</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>281</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>283</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>414</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>415</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="E35" t="s">
-        <v>284</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E36" t="s">
-        <v>286</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>287</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>288</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>421</v>
       </c>
       <c r="B39" t="s">
-        <v>289</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>290</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>292</v>
+        <v>422</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>293</v>
+        <v>423</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>294</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>424</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>425</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
+        <v>426</v>
       </c>
       <c r="E42" t="s">
-        <v>295</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>296</v>
+        <v>428</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>297</v>
+        <v>429</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="E44" t="s">
-        <v>298</v>
+        <v>430</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>273</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s">
-        <v>299</v>
+        <v>433</v>
       </c>
       <c r="C46" t="s">
-        <v>223</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="E46" t="s">
-        <v>301</v>
+        <v>434</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>435</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>436</v>
       </c>
       <c r="E47" t="s">
-        <v>303</v>
+        <v>437</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="E48" t="s">
-        <v>304</v>
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>305</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>159</v>
+        <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>439</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>366</v>
       </c>
       <c r="E49" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>307</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>435</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>358</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>311</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>313</v>
       </c>
       <c r="B53" t="s">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>313</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>444</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>445</v>
       </c>
       <c r="E54" t="s">
-        <v>106</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>372</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="E55" t="s">
-        <v>315</v>
+        <v>447</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>435</v>
       </c>
       <c r="C56" t="s">
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="E56" t="s">
-        <v>316</v>
+        <v>449</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>316</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>300</v>
       </c>
       <c r="E57" t="s">
-        <v>317</v>
+        <v>450</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s">
-        <v>318</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>320</v>
+        <v>452</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>212</v>
+        <v>17</v>
       </c>
       <c r="E59" t="s">
-        <v>321</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>455</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>424</v>
       </c>
       <c r="E60" t="s">
-        <v>323</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>403</v>
       </c>
       <c r="E61" t="s">
-        <v>324</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>326</v>
+        <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
         <v>16</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>327</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>17</v>
       </c>
       <c r="E64" t="s">
-        <v>329</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>224</v>
+        <v>271</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>331</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="B68" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E68" t="s">
-        <v>332</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>333</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>334</v>
+        <v>458</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>335</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
         <v>16</v>
@@ -4579,92 +7197,1265 @@
         <v>16</v>
       </c>
       <c r="E70" t="s">
-        <v>336</v>
+        <v>459</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>337</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E71" t="s">
-        <v>338</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>339</v>
+        <v>139</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="E72" t="s">
-        <v>340</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>341</v>
+        <v>142</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
         <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>342</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>343</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
         <v>16</v>
       </c>
       <c r="E74" t="s">
-        <v>344</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>345</v>
+        <v>146</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D75" t="s">
         <v>16</v>
       </c>
       <c r="E75" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" t="s">
+        <v>68</v>
+      </c>
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" t="s">
+        <v>68</v>
+      </c>
+      <c r="E76" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>460</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" t="s">
+        <v>68</v>
+      </c>
+      <c r="E81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>462</v>
+      </c>
+      <c r="B82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>68</v>
+      </c>
+      <c r="E82" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>160</v>
+      </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>34</v>
+      </c>
+      <c r="E83" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>464</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>170</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>325</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>327</v>
+      </c>
+      <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>172</v>
+      </c>
+      <c r="B92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" t="s">
+        <v>16</v>
+      </c>
+      <c r="D92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>329</v>
+      </c>
+      <c r="B93" t="s">
+        <v>21</v>
+      </c>
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>174</v>
+      </c>
+      <c r="B94" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>180</v>
+      </c>
+      <c r="B97" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>184</v>
+      </c>
+      <c r="B99" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>186</v>
+      </c>
+      <c r="B100" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>188</v>
+      </c>
+      <c r="B101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C101" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>466</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>468</v>
+      </c>
+      <c r="B103" t="s">
+        <v>68</v>
+      </c>
+      <c r="C103" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" t="s">
+        <v>68</v>
+      </c>
+      <c r="E103" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>470</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>192</v>
+      </c>
+      <c r="B106" t="s">
+        <v>21</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>473</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>194</v>
+      </c>
+      <c r="B108" t="s">
+        <v>21</v>
+      </c>
+      <c r="C108" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>198</v>
+      </c>
+      <c r="B109" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>200</v>
+      </c>
+      <c r="B110" t="s">
+        <v>21</v>
+      </c>
+      <c r="C110" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>202</v>
+      </c>
+      <c r="B111" t="s">
+        <v>21</v>
+      </c>
+      <c r="C111" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>204</v>
+      </c>
+      <c r="B112" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>206</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="s">
+        <v>21</v>
+      </c>
+      <c r="D113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>208</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>210</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>212</v>
+      </c>
+      <c r="B116" t="s">
+        <v>21</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>68</v>
+      </c>
+      <c r="E116" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>214</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>218</v>
+      </c>
+      <c r="B118" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>220</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>34</v>
+      </c>
+      <c r="E119" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>222</v>
+      </c>
+      <c r="B120" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" t="s">
+        <v>16</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>224</v>
+      </c>
+      <c r="B121" t="s">
+        <v>21</v>
+      </c>
+      <c r="C121" t="s">
+        <v>225</v>
+      </c>
+      <c r="D121" t="s">
+        <v>225</v>
+      </c>
+      <c r="E121" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>475</v>
+      </c>
+      <c r="B122" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" t="s">
+        <v>16</v>
+      </c>
+      <c r="D122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>227</v>
+      </c>
+      <c r="B123" t="s">
+        <v>21</v>
+      </c>
+      <c r="C123" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>229</v>
+      </c>
+      <c r="B124" t="s">
+        <v>21</v>
+      </c>
+      <c r="C124" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>231</v>
+      </c>
+      <c r="B125" t="s">
+        <v>21</v>
+      </c>
+      <c r="C125" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>233</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>237</v>
+      </c>
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>241</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" t="s">
+        <v>16</v>
+      </c>
+      <c r="E128" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>243</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>245</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>247</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
+        <v>68</v>
+      </c>
+      <c r="E131" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>249</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="s">
+        <v>16</v>
+      </c>
+      <c r="D132" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>251</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" t="s">
+        <v>16</v>
+      </c>
+      <c r="E133" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
         <v>346</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>253</v>
+      </c>
+      <c r="B135" t="s">
+        <v>21</v>
+      </c>
+      <c r="C135" t="s">
+        <v>16</v>
+      </c>
+      <c r="D135" t="s">
+        <v>16</v>
+      </c>
+      <c r="E135" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>255</v>
+      </c>
+      <c r="B136" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" t="s">
+        <v>16</v>
+      </c>
+      <c r="D136" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>481</v>
+      </c>
+      <c r="B137" t="s">
+        <v>21</v>
+      </c>
+      <c r="C137" t="s">
+        <v>16</v>
+      </c>
+      <c r="D137" t="s">
+        <v>16</v>
+      </c>
+      <c r="E137" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>257</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>259</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>261</v>
+      </c>
+      <c r="B140" t="s">
+        <v>21</v>
+      </c>
+      <c r="C140" t="s">
+        <v>16</v>
+      </c>
+      <c r="D140" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>265</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>269</v>
+      </c>
+      <c r="B144" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" t="s">
+        <v>16</v>
+      </c>
+      <c r="D144" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
